--- a/output/pdf_financials_xlsx/PNC.A.xlsx
+++ b/output/pdf_financials_xlsx/PNC.A.xlsx
@@ -1950,37 +1950,37 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>30.49</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>43.813</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>17.139</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>10.848</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>26.037</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>15.464</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>49.795</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>61.996</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>12.061</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>6.191</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.454</v>
       </c>
     </row>
     <row r="35">
@@ -2040,37 +2040,37 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>30.49</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>43.813</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>17.139</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>10.848</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>26.037</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>15.464</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>49.795</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>61.996</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>12.061</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>6.191</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>2.454</v>
       </c>
     </row>
     <row r="37">
@@ -2580,37 +2580,37 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>40.378</v>
+        <v>9.888</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>85.2</v>
+        <v>41.387</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>34.284</v>
+        <v>17.145</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>98.393</v>
+        <v>87.545</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>48.136</v>
+        <v>22.099</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>50.221</v>
+        <v>34.757</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>91.764</v>
+        <v>41.969</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>88.857</v>
+        <v>26.861</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>38.793</v>
+        <v>26.732</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>24.556</v>
+        <v>18.365</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>13.536</v>
+        <v>11.082</v>
       </c>
     </row>
     <row r="49">
@@ -5952,19 +5952,19 @@
         <v>-39.583</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>-94.761</v>
+        <v>-101.058</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>-32.305</v>
+        <v>-41.729</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>-19.754</v>
+        <v>-26.525</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>-22.629</v>
+        <v>-7.062</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-6.771</v>
       </c>
     </row>
     <row r="125">
@@ -5995,19 +5995,19 @@
         <v>-39.583</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>-94.761</v>
+        <v>-101.058</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>-32.305</v>
+        <v>-41.729</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>-19.754</v>
+        <v>-26.525</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>-22.629</v>
+        <v>-7.062</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-6.771</v>
       </c>
     </row>
     <row r="126">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -25472,7 +25472,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -26718,7 +26722,11 @@
           <t>Lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D274" t="inlineStr"/>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E274" t="inlineStr">
         <is>
           <t>-</t>
@@ -29056,7 +29064,11 @@
           <t>Lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -36264,7 +36276,7 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -37354,7 +37366,7 @@
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E419" s="5" t="n">
@@ -38804,7 +38816,7 @@
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">

--- a/output/pdf_financials_xlsx/PNC.A.xlsx
+++ b/output/pdf_financials_xlsx/PNC.A.xlsx
@@ -1295,20 +1295,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G20" s="3" t="n">
+        <v>-33.87</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>-7.067</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>-16.153</v>
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
@@ -3322,37 +3316,37 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>59.073</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>87.083</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>89.849</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>59.778</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>62.833</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>54.122</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>48.041</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0</v>
+        <v>49.599</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0</v>
+        <v>39.44</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0</v>
+        <v>35.609</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>38.509</v>
       </c>
     </row>
     <row r="65">
@@ -3457,37 +3451,37 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>40.8</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>52.977</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>47.396</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>38.771</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>44.027</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>38.768</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>32.045</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>33.955</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>18.121</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>15.928</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>19.866</v>
       </c>
     </row>
     <row r="68">
@@ -3610,19 +3604,19 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>9.481999999999999</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0</v>
+        <v>8.311999999999999</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0</v>
+        <v>8.32</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>7.773</v>
       </c>
     </row>
     <row r="71">
@@ -3655,19 +3649,19 @@
         <v>5</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>20.372</v>
+        <v>29.854</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>7.409</v>
+        <v>15.529</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>13</v>
+        <v>21.312</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>17.772</v>
+        <v>26.092</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>29.509</v>
+        <v>37.282</v>
       </c>
     </row>
     <row r="72">
@@ -3835,19 +3829,19 @@
         <v>5.893</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>16.338</v>
+        <v>6.856</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>10.377</v>
+        <v>2.257</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>12.078</v>
+        <v>3.766</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>18.521</v>
+        <v>10.201</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>26.003</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="76">
@@ -3970,19 +3964,19 @@
         <v>0</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0</v>
+        <v>37.136</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0</v>
+        <v>33.161</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0</v>
+        <v>27.749</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0</v>
+        <v>24.286</v>
       </c>
       <c r="M78" s="3" t="n">
-        <v>0</v>
+        <v>19.345</v>
       </c>
     </row>
     <row r="79">
@@ -4015,19 +4009,19 @@
         <v>250.011</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>252.983</v>
+        <v>290.119</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>248.262</v>
+        <v>281.423</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>260.909</v>
+        <v>288.658</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>292.524</v>
+        <v>316.81</v>
       </c>
       <c r="M79" s="3" t="n">
-        <v>323.129</v>
+        <v>342.474</v>
       </c>
     </row>
     <row r="80">
@@ -4060,19 +4054,19 @@
         <v>-1.86943135084414</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>-1.664545554188842</v>
+        <v>-1.948417386221091</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>-1.82999906950777</v>
+        <v>-2.125473298451804</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>-1.36116025284249</v>
+        <v>-1.540361373936551</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>-1.139512166459792</v>
+        <v>-1.259252458631099</v>
       </c>
       <c r="M80" s="3" t="n">
-        <v>-1.095758200987506</v>
+        <v>-1.180022434831785</v>
       </c>
     </row>
     <row r="81">
@@ -4285,19 +4279,19 @@
         <v>94.53700000000001</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>138.998</v>
+        <v>101.862</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>77.914</v>
+        <v>44.753</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>65.91800000000001</v>
+        <v>38.169</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>59.417</v>
+        <v>35.131</v>
       </c>
       <c r="M85" s="3" t="n">
-        <v>53.595</v>
+        <v>34.25</v>
       </c>
     </row>
     <row r="86">
@@ -5587,40 +5581,40 @@
         </is>
       </c>
       <c r="B116" s="3" t="n">
-        <v>0</v>
+        <v>-5.932</v>
       </c>
       <c r="C116" s="3" t="n">
-        <v>0</v>
+        <v>-3.109</v>
       </c>
       <c r="D116" s="3" t="n">
-        <v>0</v>
+        <v>-0.753</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-3.973</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-2.21</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-2.339</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-1.497</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.613</v>
       </c>
       <c r="J116" s="3" t="n">
-        <v>0</v>
+        <v>-0.449</v>
       </c>
       <c r="K116" s="3" t="n">
-        <v>0</v>
+        <v>-0.948</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.794</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-1.291</v>
       </c>
     </row>
     <row r="117">
@@ -7636,7 +7630,11 @@
           <t>Current portion of lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -7976,7 +7974,11 @@
           <t>Lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -9698,7 +9700,11 @@
           <t>Current portion of lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -9770,7 +9776,11 @@
           <t>Lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -12620,7 +12630,11 @@
           <t>Current portion of lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -12916,7 +12930,11 @@
           <t>Lease obligations (note 9)</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -15054,7 +15072,11 @@
           <t>Current portion of lease obligations (note 9) 9,482</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -15452,7 +15474,11 @@
           <t>Lease obligations (note 9) 37,136</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -24292,7 +24318,11 @@
           <t>Purchases of intangible assets (note 10 and 23)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -26450,7 +26480,11 @@
           <t>Purchases of intangible assets (note 11)</t>
         </is>
       </c>
-      <c r="D270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E270" t="inlineStr">
         <is>
           <t>-</t>
@@ -28550,7 +28584,11 @@
           <t>Purchases of intangible assets (note 10)</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="n">
         <v>-5.932</v>
       </c>
@@ -31514,7 +31552,11 @@
           <t>Purchases of intangible assets (note 12)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -33844,7 +33886,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E370" t="inlineStr">
         <is>
           <t>-</t>
@@ -41752,7 +41798,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E479" t="inlineStr">
         <is>
           <t>-</t>
